--- a/ProyectoAsistencia/ReporteHorarioLaboratorio.xlsx
+++ b/ProyectoAsistencia/ReporteHorarioLaboratorio.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="41">
   <si>
     <t>Laboratorio</t>
   </si>
@@ -35,55 +35,106 @@
     <t>Código de Horario</t>
   </si>
   <si>
+    <t>LAB-101</t>
+  </si>
+  <si>
+    <t>Análisis y Diseño de Sistemas</t>
+  </si>
+  <si>
+    <t>martinmoreno</t>
+  </si>
+  <si>
+    <t>JUEVES</t>
+  </si>
+  <si>
+    <t>08:00:00</t>
+  </si>
+  <si>
+    <t>10:00:00</t>
+  </si>
+  <si>
+    <t>HS19</t>
+  </si>
+  <si>
+    <t>LAB-102</t>
+  </si>
+  <si>
+    <t>Administración de Proyectos de Software</t>
+  </si>
+  <si>
+    <t>paulamunoz</t>
+  </si>
+  <si>
+    <t>12:00:00</t>
+  </si>
+  <si>
+    <t>HS20</t>
+  </si>
+  <si>
     <t>LAB-103</t>
   </si>
   <si>
-    <t>Programación I</t>
-  </si>
-  <si>
-    <t>laurafernandez</t>
-  </si>
-  <si>
-    <t>MARTES</t>
-  </si>
-  <si>
-    <t>12:00:00</t>
+    <t>Inteligencia Artificial</t>
+  </si>
+  <si>
+    <t>antoniomendez</t>
   </si>
   <si>
     <t>14:00:00</t>
   </si>
   <si>
-    <t>HS09</t>
-  </si>
-  <si>
-    <t>cesarrojas</t>
-  </si>
-  <si>
-    <t>DOMINGO</t>
-  </si>
-  <si>
-    <t>HS39</t>
+    <t>HS21</t>
   </si>
   <si>
     <t>LAB-104</t>
   </si>
   <si>
-    <t>Programación II</t>
-  </si>
-  <si>
-    <t>miguelsanchez</t>
+    <t>Teoría de la Computación</t>
+  </si>
+  <si>
+    <t>claraserrano</t>
   </si>
   <si>
     <t>16:00:00</t>
   </si>
   <si>
-    <t>HS10</t>
-  </si>
-  <si>
-    <t>gabrielagonzalez</t>
-  </si>
-  <si>
-    <t>HS40</t>
+    <t>HS22</t>
+  </si>
+  <si>
+    <t>LAB-105</t>
+  </si>
+  <si>
+    <t>Ingeniería de Requerimientos</t>
+  </si>
+  <si>
+    <t>fernandoortiz</t>
+  </si>
+  <si>
+    <t>18:00:00</t>
+  </si>
+  <si>
+    <t>HS23</t>
+  </si>
+  <si>
+    <t>Laboratorio orrai</t>
+  </si>
+  <si>
+    <t>Como tener armadura gelatinosa</t>
+  </si>
+  <si>
+    <t>Orrai</t>
+  </si>
+  <si>
+    <t>Jueves</t>
+  </si>
+  <si>
+    <t>06:00</t>
+  </si>
+  <si>
+    <t>12:00</t>
+  </si>
+  <si>
+    <t>laboratorio_orrai_jueves_orrai_como_tener_armadura_gelatinosa_6y00_12y00</t>
   </si>
 </sst>
 </file>
@@ -128,7 +179,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.0" customWidth="true"/>
@@ -188,71 +239,117 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" t="s">
         <v>17</v>
       </c>
-      <c r="B4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" t="s">
-        <v>12</v>
-      </c>
       <c r="F4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" t="s">
         <v>22</v>
       </c>
-      <c r="D5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" t="s">
-        <v>12</v>
-      </c>
       <c r="F5" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G5" t="s">
-        <v>23</v>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G7" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
